--- a/data.mn/public/datasets/meat-production-historical-by-type.xlsx
+++ b/data.mn/public/datasets/meat-production-historical-by-type.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,451 +414,1049 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Meat Type</t>
+          <t>year</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="E1" t="n">
-        <v>1961</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1962</v>
-      </c>
-      <c r="G1" t="n">
-        <v>1963</v>
-      </c>
-      <c r="H1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="I1" t="n">
-        <v>1965</v>
-      </c>
-      <c r="J1" t="n">
-        <v>1966</v>
-      </c>
-      <c r="K1" t="n">
-        <v>1967</v>
-      </c>
-      <c r="L1" t="n">
-        <v>1968</v>
-      </c>
-      <c r="M1" t="n">
-        <v>1969</v>
-      </c>
-      <c r="N1" t="n">
-        <v>1970</v>
-      </c>
-      <c r="O1" t="n">
-        <v>1971</v>
-      </c>
-      <c r="P1" t="n">
-        <v>1972</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>1973</v>
-      </c>
-      <c r="R1" t="n">
-        <v>1974</v>
-      </c>
-      <c r="S1" t="n">
-        <v>1975</v>
-      </c>
-      <c r="T1" t="n">
-        <v>1976</v>
-      </c>
-      <c r="U1" t="n">
-        <v>1977</v>
-      </c>
-      <c r="V1" t="n">
-        <v>1978</v>
-      </c>
-      <c r="W1" t="n">
-        <v>1979</v>
-      </c>
-      <c r="X1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>1981</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>1982</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>1983</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>1984</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>1985</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>1986</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>1987</v>
-      </c>
-      <c r="AF1" t="n">
-        <v>1988</v>
-      </c>
-      <c r="AG1" t="n">
-        <v>1989</v>
-      </c>
-      <c r="AH1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="AI1" t="n">
-        <v>1991</v>
-      </c>
-      <c r="AJ1" t="n">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Beef</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>52</v>
-      </c>
-      <c r="M2" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>75.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Mutton and goat meat</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="D3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="N3" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="R3" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>132.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="U3" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="V3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>118.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>132</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>123.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>112.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>135.9</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>116.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Pork</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B3" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B4" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>96.2</v>
+      </c>
       <c r="D4" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.4</v>
       </c>
-      <c r="F4" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B6" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B7" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.3</v>
       </c>
-      <c r="H4" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.3</v>
       </c>
-      <c r="I4" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B9" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B10" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K4" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.3</v>
       </c>
-      <c r="L4" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B12" t="n">
+        <v>52</v>
+      </c>
+      <c r="C12" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.4</v>
       </c>
-      <c r="M4" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B13" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.4</v>
       </c>
-      <c r="N4" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B14" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.3</v>
       </c>
-      <c r="O4" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B15" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.4</v>
       </c>
-      <c r="P4" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q4" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B17" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.5</v>
       </c>
-      <c r="R4" t="n">
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B18" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.5</v>
       </c>
-      <c r="S4" t="n">
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B19" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.6</v>
       </c>
-      <c r="T4" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B20" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.5</v>
       </c>
-      <c r="U4" t="n">
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B21" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.4</v>
       </c>
-      <c r="V4" t="n">
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B22" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.6</v>
       </c>
-      <c r="W4" t="n">
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B23" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.9</v>
       </c>
-      <c r="X4" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B24" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B25" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z4" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B26" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>132</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA4" t="n">
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B27" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB4" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B28" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC4" t="n">
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B29" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D29" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD4" t="n">
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B30" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="D30" t="n">
         <v>2.4</v>
       </c>
-      <c r="AE4" t="n">
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B31" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="D31" t="n">
         <v>3.1</v>
       </c>
-      <c r="AF4" t="n">
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D32" t="n">
         <v>4</v>
       </c>
-      <c r="AG4" t="n">
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B33" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D33" t="n">
         <v>5.5</v>
       </c>
-      <c r="AH4" t="n">
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B34" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="D34" t="n">
         <v>7.9</v>
       </c>
-      <c r="AI4" t="n">
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="D35" t="n">
         <v>3.8</v>
       </c>
-      <c r="AJ4" t="n">
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Гахайн мах</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Хонь, ямааны мах</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Үхрийн мах</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>65.09999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>132</v>
+      </c>
+      <c r="D26" t="n">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>75.7</v>
       </c>
     </row>
   </sheetData>
